--- a/artfynd/A 27375-2024 artfynd.xlsx
+++ b/artfynd/A 27375-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132491582</v>
       </c>
       <c r="B2" t="n">
-        <v>57100</v>
+        <v>57101</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 27375-2024 artfynd.xlsx
+++ b/artfynd/A 27375-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132491582</v>
       </c>
       <c r="B2" t="n">
-        <v>57101</v>
+        <v>57105</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 27375-2024 artfynd.xlsx
+++ b/artfynd/A 27375-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,62 +675,59 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132491582</v>
+        <v>91190541</v>
       </c>
       <c r="B2" t="n">
-        <v>57108</v>
+        <v>84147</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102932</v>
+        <v>1444</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kricka</t>
+          <t>Scharlakansvårskål agg.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Anas crecca</t>
+          <t>Sarcoscypha coccinea s.lat.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Jacq.:Fr.) Lambotte</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Värmlandsmossen våtmark 4, Srm</t>
+          <t>Krämbolsskogen, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>565022</v>
+        <v>565136</v>
       </c>
       <c r="R2" t="n">
-        <v>6540073</v>
+        <v>6539981</v>
       </c>
       <c r="S2" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,45 +751,298 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2021-02-26</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2021-02-26</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Kanske troligast Sarcoscypha austriaca?</t>
         </is>
       </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Sank blandskog, funnen på sälglåga i liten vårbäck</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Hanna Stahle</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Hanna Stahle</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>132491582</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57125</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>102932</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Kricka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Anas crecca</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Värmlandsmossen våtmark 4, Srm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>565022</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6540073</v>
+      </c>
+      <c r="S3" t="n">
+        <v>75</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Östra Vingåker</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>09:47</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>09:47</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Stephan Gäfvert</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Stephan Gäfvert</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>132491769</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58837</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>208250</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Åkergroda</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Rana arvalis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Värmlandsmossen våtmark 4, Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>565012</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6540128</v>
+      </c>
+      <c r="S4" t="n">
+        <v>20</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Östra Vingåker</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>09:47</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>09:47</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Stephan Gäfvert</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Stephan Gäfvert</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 27375-2024 artfynd.xlsx
+++ b/artfynd/A 27375-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -806,6 +811,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91190541</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -927,6 +937,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132491582</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1043,8 +1058,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132491769</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>